--- a/paper/figures/data/all_statistics.xlsx
+++ b/paper/figures/data/all_statistics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/umutcaginozcan/Desktop/NICU Breastfeeding Paper/paper/figures/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0188B611-CD3A-3B46-9CDC-733859A8FE6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEEF8666-7B87-4744-8F73-B0C30BD5DF33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="41120" windowHeight="24100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="41120" windowHeight="24100" firstSheet="4" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GA_Descriptive" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,23 @@
     <sheet name="GA_Normality" sheetId="3" r:id="rId3"/>
     <sheet name="GA_Pairwise_Comparisons" sheetId="4" r:id="rId4"/>
     <sheet name="GA_Clinical_Categories" sheetId="5" r:id="rId5"/>
-    <sheet name="LOS_Descriptive" sheetId="7" r:id="rId6"/>
-    <sheet name="LOS_Statistical_Tests" sheetId="8" r:id="rId7"/>
-    <sheet name="LOS_Normality" sheetId="9" r:id="rId8"/>
-    <sheet name="LOS_Pairwise" sheetId="10" r:id="rId9"/>
+    <sheet name="LOS_Descriptive" sheetId="6" r:id="rId6"/>
+    <sheet name="LOS_Statistical_Tests" sheetId="7" r:id="rId7"/>
+    <sheet name="LOS_Normality" sheetId="8" r:id="rId8"/>
+    <sheet name="LOS_Pairwise" sheetId="9" r:id="rId9"/>
+    <sheet name="Feeding_Trajectories" sheetId="10" r:id="rId10"/>
+    <sheet name="Trajectories_Within_Group" sheetId="11" r:id="rId11"/>
+    <sheet name="Trajectories_Between_Group" sheetId="12" r:id="rId12"/>
+    <sheet name="BM_Trajectories" sheetId="13" r:id="rId13"/>
+    <sheet name="Formula_Trajectories" sheetId="14" r:id="rId14"/>
+    <sheet name="Mixed_Composition" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="113">
   <si>
     <t>Feeding Type</t>
   </si>
@@ -252,20 +258,140 @@
     <t>Effect size (r)</t>
   </si>
   <si>
-    <t>s</t>
+    <t>Timepoint</t>
+  </si>
+  <si>
+    <t>Day 1</t>
+  </si>
+  <si>
+    <t>48.0 ± 75.9</t>
+  </si>
+  <si>
+    <t>0.0 (0.0–88.0)</t>
+  </si>
+  <si>
+    <t>Day 2</t>
+  </si>
+  <si>
+    <t>176.1 ± 163.3</t>
+  </si>
+  <si>
+    <t>160.0 (24.0–276.0)</t>
+  </si>
+  <si>
+    <t>Day 3</t>
+  </si>
+  <si>
+    <t>185.5 ± 166.4</t>
+  </si>
+  <si>
+    <t>176.0 (32.0–300.0)</t>
+  </si>
+  <si>
+    <t>Discharge</t>
+  </si>
+  <si>
+    <t>411.5 ± 268.9</t>
+  </si>
+  <si>
+    <t>374.0 (308.0–460.0)</t>
+  </si>
+  <si>
+    <t>125.3 ± 108.9</t>
+  </si>
+  <si>
+    <t>120.0 (23.8–190.0)</t>
+  </si>
+  <si>
+    <t>205.8 ± 148.0</t>
+  </si>
+  <si>
+    <t>198.0 (89.0–267.2)</t>
+  </si>
+  <si>
+    <t>223.5 ± 159.6</t>
+  </si>
+  <si>
+    <t>224.0 (103.9–316.2)</t>
+  </si>
+  <si>
+    <t>406.9 ± 200.8</t>
+  </si>
+  <si>
+    <t>380.0 (314.2–477.0)</t>
+  </si>
+  <si>
+    <t>143.6 ± 134.9</t>
+  </si>
+  <si>
+    <t>130.0 (43.0–200.0)</t>
+  </si>
+  <si>
+    <t>198.2 ± 133.9</t>
+  </si>
+  <si>
+    <t>208.0 (103.6–258.0)</t>
+  </si>
+  <si>
+    <t>220.5 ± 139.2</t>
+  </si>
+  <si>
+    <t>222.0 (120.0–300.0)</t>
+  </si>
+  <si>
+    <t>384.4 ± 124.1</t>
+  </si>
+  <si>
+    <t>400.0 (300.0–426.0)</t>
+  </si>
+  <si>
+    <t>n (complete cases)</t>
+  </si>
+  <si>
+    <t>Significant</t>
+  </si>
+  <si>
+    <t>Friedman</t>
+  </si>
+  <si>
+    <t>H-statistic</t>
+  </si>
+  <si>
+    <t>Exclusive BF (cc)</t>
+  </si>
+  <si>
+    <t>Formula (cc)</t>
+  </si>
+  <si>
+    <t>Mixed (cc)</t>
+  </si>
+  <si>
+    <t>Breast Milk (cc)</t>
+  </si>
+  <si>
+    <t>Total (cc)</t>
+  </si>
+  <si>
+    <t>BM Percentage (%)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -282,7 +408,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -305,13 +431,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -692,6 +836,677 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2">
+        <v>747</v>
+      </c>
+      <c r="D2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3">
+        <v>747</v>
+      </c>
+      <c r="D3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4">
+        <v>747</v>
+      </c>
+      <c r="D4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5">
+        <v>747</v>
+      </c>
+      <c r="D5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6">
+        <v>280</v>
+      </c>
+      <c r="D6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7">
+        <v>280</v>
+      </c>
+      <c r="D7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8">
+        <v>280</v>
+      </c>
+      <c r="D8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9">
+        <v>280</v>
+      </c>
+      <c r="D9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>747</v>
+      </c>
+      <c r="C2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2">
+        <v>1668.8475433526021</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>280</v>
+      </c>
+      <c r="C3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3">
+        <v>605.85595463138009</v>
+      </c>
+      <c r="E3">
+        <v>5.4186468936273089E-131</v>
+      </c>
+      <c r="F3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4">
+        <v>83.527220630372526</v>
+      </c>
+      <c r="E4">
+        <v>5.3735055532931913E-18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <v>163.94156762274201</v>
+      </c>
+      <c r="D2">
+        <v>2.5150169332072338E-36</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>11.2715712928906</v>
+      </c>
+      <c r="D3">
+        <v>3.5678730450371351E-3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>12.06125190822585</v>
+      </c>
+      <c r="D4">
+        <v>2.4039887209302432E-3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>0.64058437438920857</v>
+      </c>
+      <c r="D5">
+        <v>0.72593689661755545</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2">
+        <v>42.790495314591702</v>
+      </c>
+      <c r="C2">
+        <v>31.491785714285719</v>
+      </c>
+      <c r="D2">
+        <v>7.1891891891891886</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3">
+        <v>78.942436412315928</v>
+      </c>
+      <c r="C3">
+        <v>61.417857142857137</v>
+      </c>
+      <c r="D3">
+        <v>18.810810810810811</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4">
+        <v>105.4484605087015</v>
+      </c>
+      <c r="C4">
+        <v>81.817857142857136</v>
+      </c>
+      <c r="D4">
+        <v>27.351351351351351</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5">
+        <v>220.27771084337351</v>
+      </c>
+      <c r="C5">
+        <v>186.45</v>
+      </c>
+      <c r="D5">
+        <v>66.945945945945951</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2">
+        <v>47.967871485943768</v>
+      </c>
+      <c r="C2">
+        <v>125.2657142857143</v>
+      </c>
+      <c r="D2">
+        <v>143.56756756756761</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3">
+        <v>43.233601070950471</v>
+      </c>
+      <c r="C3">
+        <v>129.3821428571429</v>
+      </c>
+      <c r="D3">
+        <v>175.17567567567571</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4">
+        <v>37.870161290322592</v>
+      </c>
+      <c r="C4">
+        <v>130.76821428571429</v>
+      </c>
+      <c r="D4">
+        <v>190.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5">
+        <v>14.13520749665328</v>
+      </c>
+      <c r="C5">
+        <v>177.41785714285709</v>
+      </c>
+      <c r="D5">
+        <v>301.18918918918922</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2">
+        <v>7.1891891891891886</v>
+      </c>
+      <c r="C2">
+        <v>143.56756756756761</v>
+      </c>
+      <c r="D2">
+        <v>150.7567567567568</v>
+      </c>
+      <c r="E2">
+        <v>4.7687343133739688</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3">
+        <v>18.810810810810811</v>
+      </c>
+      <c r="C3">
+        <v>175.17567567567571</v>
+      </c>
+      <c r="D3">
+        <v>193.98648648648651</v>
+      </c>
+      <c r="E3">
+        <v>9.6969696969696972</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4">
+        <v>27.351351351351351</v>
+      </c>
+      <c r="C4">
+        <v>190.2</v>
+      </c>
+      <c r="D4">
+        <v>217.55135135135129</v>
+      </c>
+      <c r="E4">
+        <v>12.57236564215966</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5">
+        <v>66.945945945945951</v>
+      </c>
+      <c r="C5">
+        <v>301.18918918918922</v>
+      </c>
+      <c r="D5">
+        <v>368.1351351351351</v>
+      </c>
+      <c r="E5">
+        <v>18.185155274943099</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D5"/>
@@ -1058,8 +1873,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:T47"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -1128,11 +1943,6 @@
       </c>
       <c r="E4" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="47" spans="20:20" x14ac:dyDescent="0.2">
-      <c r="T47" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1141,7 +1951,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -1221,90 +2031,90 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2">
+        <v>0.63017547130584717</v>
+      </c>
+      <c r="D2">
+        <v>3.3874430799279941E-37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3">
+        <v>0.50715756416320801</v>
+      </c>
+      <c r="D3">
+        <v>3.1218669582336002E-27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4">
+        <v>0.59119004011154175</v>
+      </c>
+      <c r="D4">
+        <v>5.8920925916083888E-9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2">
-        <v>0.63017547130584717</v>
-      </c>
-      <c r="D2">
-        <v>3.3874430799279941E-37</v>
-      </c>
-      <c r="E2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3">
-        <v>0.50715756416320801</v>
-      </c>
-      <c r="D3">
-        <v>3.1218669582336002E-27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4">
-        <v>0.59119004011154175</v>
-      </c>
-      <c r="D4">
-        <v>5.8920925916083888E-9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
